--- a/public/Master Season.xlsx
+++ b/public/Master Season.xlsx
@@ -41,40 +41,40 @@
     <t>Season year</t>
   </si>
   <si>
-    <t>SE00001</t>
-  </si>
-  <si>
-    <t>SPR</t>
-  </si>
-  <si>
-    <t>SE00002</t>
-  </si>
-  <si>
-    <t>SUM</t>
-  </si>
-  <si>
-    <t>SE00003</t>
-  </si>
-  <si>
-    <t>WIN</t>
-  </si>
-  <si>
-    <t>SE00004</t>
-  </si>
-  <si>
-    <t>FAL</t>
-  </si>
-  <si>
-    <t>SE00005</t>
-  </si>
-  <si>
-    <t>SE00006</t>
-  </si>
-  <si>
-    <t>SE00007</t>
-  </si>
-  <si>
-    <t>SE00008</t>
+    <t>SEA000000001</t>
+  </si>
+  <si>
+    <t>SPRING</t>
+  </si>
+  <si>
+    <t>SEA000000002</t>
+  </si>
+  <si>
+    <t>SUMMER</t>
+  </si>
+  <si>
+    <t>SEA000000003</t>
+  </si>
+  <si>
+    <t>WINTER</t>
+  </si>
+  <si>
+    <t>SEA000000004</t>
+  </si>
+  <si>
+    <t>FALL</t>
+  </si>
+  <si>
+    <t>SEA000000005</t>
+  </si>
+  <si>
+    <t>SEA000000006</t>
+  </si>
+  <si>
+    <t>SEA000000007</t>
+  </si>
+  <si>
+    <t>SEA000000008</t>
   </si>
 </sst>
 </file>
@@ -87,14 +87,7 @@
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -550,153 +543,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1019,6 +1013,10 @@
   <sheetPr/>
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="14.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="11.2857142857143" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -1038,13 +1036,13 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>2024</v>
       </c>
     </row>
@@ -1052,13 +1050,13 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>2024</v>
       </c>
     </row>
@@ -1066,13 +1064,13 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>2024</v>
       </c>
     </row>
@@ -1080,13 +1078,13 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>2024</v>
       </c>
     </row>
@@ -1094,13 +1092,13 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
         <v>2025</v>
       </c>
     </row>
@@ -1108,13 +1106,13 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="2">
         <v>2025</v>
       </c>
     </row>
@@ -1122,13 +1120,13 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="2">
         <v>2025</v>
       </c>
     </row>
@@ -1136,13 +1134,13 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="2">
         <v>2025</v>
       </c>
     </row>
